--- a/Corner_EV_Ledger.xlsx
+++ b/Corner_EV_Ledger.xlsx
@@ -3707,14 +3707,38 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="6" t="n"/>
+      <c r="A57" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Liverpool v Ipswich</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>1.8</v>
+      </c>
       <c r="I57" s="7">
         <f>IF(OR(G57="",H57=""),"",H57/G57-1)</f>
         <v/>
@@ -3726,7 +3750,11 @@
       </c>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="9" t="n"/>
-      <c r="N57" s="10" t="n"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>Skybet</t>
+        </is>
+      </c>
       <c r="O57" s="11">
         <f>IF(OR(I57="",I57&lt;=0,H57&lt;=1),"",MIN(I57/(H57-1),Summary!$B$32)*Summary!$B$31*Summary!$B$30)</f>
         <v/>
@@ -3737,14 +3765,30 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
+      <c r="A58" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>VfL Wolfsburg II v Energie Cottbus</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Over 11 Asian Corners</t>
+        </is>
+      </c>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="5" t="n"/>
-      <c r="H58" s="6" t="n"/>
+      <c r="H58" s="6" t="n">
+        <v>1.925</v>
+      </c>
       <c r="I58" s="7">
         <f>IF(OR(G58="",H58=""),"",H58/G58-1)</f>
         <v/>
@@ -3756,7 +3800,11 @@
       </c>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="9" t="n"/>
-      <c r="N58" s="10" t="n"/>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>Asian line — no fair price yet. League inferred, please confirm.</t>
+        </is>
+      </c>
       <c r="O58" s="11">
         <f>IF(OR(I58="",I58&lt;=0,H58&lt;=1),"",MIN(I58/(H58-1),Summary!$B$32)*Summary!$B$31*Summary!$B$30)</f>
         <v/>
@@ -3767,14 +3815,34 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
+      <c r="A59" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>RB Bragantino v Bahia</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>RB Bragantino</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="n"/>
-      <c r="F59" s="3" t="n"/>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="G59" s="5" t="n"/>
-      <c r="H59" s="6" t="n"/>
+      <c r="H59" s="6" t="n">
+        <v>1.83</v>
+      </c>
       <c r="I59" s="7">
         <f>IF(OR(G59="",H59=""),"",H59/G59-1)</f>
         <v/>
@@ -3786,7 +3854,11 @@
       </c>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="9" t="n"/>
-      <c r="N59" s="10" t="n"/>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>Bet365. No projection yet.</t>
+        </is>
+      </c>
       <c r="O59" s="11">
         <f>IF(OR(I59="",I59&lt;=0,H59&lt;=1),"",MIN(I59/(H59-1),Summary!$B$32)*Summary!$B$31*Summary!$B$30)</f>
         <v/>
@@ -3797,14 +3869,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
+      <c r="A60" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Turkey Super Lig</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Fenerbahce v Besiktas</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="n"/>
-      <c r="F60" s="3" t="n"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
       <c r="G60" s="5" t="n"/>
-      <c r="H60" s="6" t="n"/>
+      <c r="H60" s="6" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I60" s="7">
         <f>IF(OR(G60="",H60=""),"",H60/G60-1)</f>
         <v/>
@@ -3816,7 +3908,11 @@
       </c>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="9" t="n"/>
-      <c r="N60" s="10" t="n"/>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>No projection yet.</t>
+        </is>
+      </c>
       <c r="O60" s="11">
         <f>IF(OR(I60="",I60&lt;=0,H60&lt;=1),"",MIN(I60/(H60-1),Summary!$B$32)*Summary!$B$31*Summary!$B$30)</f>
         <v/>
@@ -3827,14 +3923,34 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
+      <c r="A61" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Ceara v Sport Recife</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Ceara</t>
+        </is>
+      </c>
       <c r="E61" s="4" t="n"/>
-      <c r="F61" s="3" t="n"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="G61" s="5" t="n"/>
-      <c r="H61" s="6" t="n"/>
+      <c r="H61" s="6" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I61" s="7">
         <f>IF(OR(G61="",H61=""),"",H61/G61-1)</f>
         <v/>
@@ -3846,7 +3962,11 @@
       </c>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="9" t="n"/>
-      <c r="N61" s="10" t="n"/>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>No projection yet.</t>
+        </is>
+      </c>
       <c r="O61" s="11">
         <f>IF(OR(I61="",I61&lt;=0,H61&lt;=1),"",MIN(I61/(H61-1),Summary!$B$32)*Summary!$B$31*Summary!$B$30)</f>
         <v/>
@@ -3857,14 +3977,34 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
+      <c r="A62" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Vancouver v Atlanta</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
       <c r="E62" s="4" t="n"/>
-      <c r="F62" s="3" t="n"/>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
       <c r="G62" s="5" t="n"/>
-      <c r="H62" s="6" t="n"/>
+      <c r="H62" s="6" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I62" s="7">
         <f>IF(OR(G62="",H62=""),"",H62/G62-1)</f>
         <v/>
@@ -3876,7 +4016,11 @@
       </c>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="9" t="n"/>
-      <c r="N62" s="10" t="n"/>
+      <c r="N62" s="10" t="inlineStr">
+        <is>
+          <t>No projection yet.</t>
+        </is>
+      </c>
       <c r="O62" s="11">
         <f>IF(OR(I62="",I62&lt;=0,H62&lt;=1),"",MIN(I62/(H62-1),Summary!$B$32)*Summary!$B$31*Summary!$B$30)</f>
         <v/>
@@ -3887,14 +4031,34 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
+      <c r="A63" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Botafogo v Palmeiras</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
       <c r="E63" s="4" t="n"/>
-      <c r="F63" s="3" t="n"/>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="G63" s="5" t="n"/>
-      <c r="H63" s="6" t="n"/>
+      <c r="H63" s="6" t="n">
+        <v>2.25</v>
+      </c>
       <c r="I63" s="7">
         <f>IF(OR(G63="",H63=""),"",H63/G63-1)</f>
         <v/>
@@ -3906,7 +4070,11 @@
       </c>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="9" t="n"/>
-      <c r="N63" s="10" t="n"/>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>No projection yet.</t>
+        </is>
+      </c>
       <c r="O63" s="11">
         <f>IF(OR(I63="",I63&lt;=0,H63&lt;=1),"",MIN(I63/(H63-1),Summary!$B$32)*Summary!$B$31*Summary!$B$30)</f>
         <v/>
